--- a/templates/31-observation-template.xlsx
+++ b/templates/31-observation-template.xlsx
@@ -2,8 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Blank template" sheetId="2" r:id="rId2"/>
+    <sheet name="Blank template" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -448,114 +447,6 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="92" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10.31  Observation</t>
-        </is>
-      </c>
-      <c r="B1" s="5"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Elicitation and collaboration</t>
-        </is>
-      </c>
-      <c r="B2" s="8"/>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">What it is for</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Studies work as it is actually performed, rather than as it is described.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reach for it when</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reach for it when what people say they do and what the system records do not agree, or when the work is tacit and hard to articulate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confused with</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Observation elicits from the work itself; interviews elicit from the person. If the scenario stresses that the documented procedure is not being followed, the answer is almost always observation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tasks</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 Conduct Elicitation  ·  6.1 Analyze Current State  ·  8.3 Assess Solution Limitations</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Knowledge areas</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4, 6, 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The blank template is on the next sheet — fill it in.</t>
-        </is>
-      </c>
-      <c r="B10" s="6"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A10:B10"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
@@ -612,21 +503,106 @@
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
     </row>
-    <row r="8"/>
+    <row r="8">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+    </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">One row per documented step.</t>
         </is>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A26:C26"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
